--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B190F-165F-46F2-A4F4-77062A34D0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E222523-238B-4EA9-9BF0-AC26FDEDC45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 19-12-2025'!$A$1:$K$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 29-01-2026'!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E222523-238B-4EA9-9BF0-AC26FDEDC45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31691E7-90E7-4632-8D31-D2A5054D48AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 29-01-2026'!$A$1:$K$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 02-02-2026'!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31691E7-90E7-4632-8D31-D2A5054D48AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0FC10F-9260-40B1-9B75-E2B7973824CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 02-02-2026'!$A$1:$K$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 20-02-2026'!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -623,9 +623,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -677,7 +677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -709,7 +709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -744,7 +744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -810,7 +810,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -842,7 +842,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -926,7 +926,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -958,7 +958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -981,7 +981,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>84</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0FC10F-9260-40B1-9B75-E2B7973824CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF45A454-9A5E-463C-AB68-2CAF650D1CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 20-02-2026'!$A$1:$K$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 04-03-2026'!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF45A454-9A5E-463C-AB68-2CAF650D1CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7BB3D-5B0A-4FA3-806C-962313D9EFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 04-03-2026'!$A$1:$K$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 06-03-2026'!$A$1:$K$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="87">
   <si>
     <t>Standard</t>
   </si>
@@ -98,6 +98,10 @@
   </si>
   <si>
     <t>CareCommunication (4.0)</t>
+  </si>
+  <si>
+    <t>CareCommunication (5.0_x000D_
+5.0)</t>
   </si>
   <si>
     <t>Care Plan</t>
@@ -622,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -798,21 +802,21 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="K7" t="s">
-        <v>18</v>
+      <c r="I7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -820,42 +824,21 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
         <v>14</v>
       </c>
       <c r="F9" t="s">
@@ -879,10 +862,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
@@ -914,88 +897,97 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
         <v>32</v>
       </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
       <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -1004,110 +996,101 @@
         <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
         <v>40</v>
       </c>
-      <c r="B15" t="s">
-        <v>41</v>
-      </c>
       <c r="C15" t="s">
         <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>14</v>
+      <c r="I16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
       </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
       <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -1139,10 +1122,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -1174,10 +1157,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
         <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>53</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
@@ -1209,11 +1192,11 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -1221,7 +1204,7 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
@@ -1230,6 +1213,9 @@
         <v>14</v>
       </c>
       <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" t="s">
         <v>14</v>
       </c>
       <c r="J22" t="s">
@@ -1241,7 +1227,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
         <v>56</v>
@@ -1253,7 +1239,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
@@ -1262,9 +1248,6 @@
         <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" t="s">
         <v>14</v>
       </c>
       <c r="J23" t="s">
@@ -1276,10 +1259,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
         <v>57</v>
-      </c>
-      <c r="B24" t="s">
-        <v>58</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -1311,10 +1294,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
         <v>59</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -1346,10 +1329,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
         <v>61</v>
-      </c>
-      <c r="B26" t="s">
-        <v>62</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -1381,10 +1364,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
         <v>63</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -1416,16 +1399,19 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
         <v>65</v>
       </c>
-      <c r="B28" t="s">
-        <v>66</v>
-      </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
@@ -1448,20 +1434,17 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
         <v>67</v>
       </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
       </c>
-      <c r="E29" t="s">
-        <v>14</v>
-      </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
@@ -1472,7 +1455,7 @@
         <v>14</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J29" t="s">
         <v>14</v>
@@ -1483,44 +1466,56 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
         <v>69</v>
       </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
       <c r="C30" t="s">
         <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
       </c>
+      <c r="J30" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
         <v>71</v>
       </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
-      <c r="D31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" t="s">
-        <v>14</v>
+      <c r="I31" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
         <v>73</v>
@@ -1528,59 +1523,53 @@
       <c r="C32" t="s">
         <v>13</v>
       </c>
-      <c r="I32" t="s">
-        <v>15</v>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" t="s">
-        <v>75</v>
-      </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="I33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s">
         <v>76</v>
       </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
       <c r="C34" t="s">
         <v>13</v>
       </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" t="s">
+      <c r="I34" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
         <v>78</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -1606,85 +1595,114 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
         <v>80</v>
       </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
-      <c r="I36" t="s">
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" t="s">
         <v>82</v>
       </c>
-      <c r="B37" t="s">
-        <v>83</v>
-      </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" t="s">
-        <v>14</v>
-      </c>
       <c r="I37" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
         <v>84</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>85</v>
       </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7BB3D-5B0A-4FA3-806C-962313D9EFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2718BCAC-5988-4A5E-9B3B-846EBF7DF331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2718BCAC-5988-4A5E-9B3B-846EBF7DF331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6593744-F0A3-450B-B7BB-17760D083A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6593744-F0A3-450B-B7BB-17760D083A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8ECEBA-80EE-43CE-8277-506B36F6415A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 06-03-2026'!$A$1:$K$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 09-03-2026'!$A$1:$K$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8ECEBA-80EE-43CE-8277-506B36F6415A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A50A23-C0DE-4A9A-A126-15EC935840AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A50A23-C0DE-4A9A-A126-15EC935840AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3F1F13-F477-45B6-9411-7E178FD2BB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 09-03-2026'!$A$1:$K$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 11-03-2026'!$A$1:$K$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="87">
   <si>
     <t>Standard</t>
   </si>
@@ -706,6 +706,9 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
       <c r="J3" t="s">
         <v>14</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3F1F13-F477-45B6-9411-7E178FD2BB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D505BD71-3741-414F-932E-9D79F8F86E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 11-03-2026'!$A$1:$K$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 11-03-2026'!$A$1:$K$37</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
   <si>
     <t>Standard</t>
   </si>
@@ -149,12 +149,6 @@
     <t>DIS07 (D0734L)</t>
   </si>
   <si>
-    <t>Psykologepikrise</t>
-  </si>
-  <si>
-    <t>DIS10 (D1034L)</t>
-  </si>
-  <si>
     <t>Bookingsvar</t>
   </si>
   <si>
@@ -234,12 +228,6 @@
   </si>
   <si>
     <t>RUC02 (U0231U)</t>
-  </si>
-  <si>
-    <t>Psykologafregning</t>
-  </si>
-  <si>
-    <t>RUC10 (U1031U)</t>
   </si>
   <si>
     <t>Sundhedsjournal</t>
@@ -626,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1047,8 +1035,11 @@
       <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="I16" t="s">
-        <v>15</v>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1061,10 +1052,13 @@
       <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1081,10 +1075,25 @@
       <c r="D18" t="s">
         <v>14</v>
       </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
       <c r="H18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1207,7 +1216,7 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
@@ -1216,9 +1225,6 @@
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" t="s">
         <v>14</v>
       </c>
       <c r="J22" t="s">
@@ -1230,11 +1236,11 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
         <v>55</v>
       </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
@@ -1242,7 +1248,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
@@ -1251,6 +1257,9 @@
         <v>14</v>
       </c>
       <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" t="s">
         <v>14</v>
       </c>
       <c r="J23" t="s">
@@ -1262,7 +1271,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
         <v>57</v>
@@ -1413,9 +1422,6 @@
       <c r="D28" t="s">
         <v>14</v>
       </c>
-      <c r="E28" t="s">
-        <v>18</v>
-      </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
@@ -1448,6 +1454,9 @@
       <c r="D29" t="s">
         <v>14</v>
       </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
@@ -1458,7 +1467,7 @@
         <v>14</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J29" t="s">
         <v>14</v>
@@ -1480,20 +1489,8 @@
       <c r="D30" t="s">
         <v>14</v>
       </c>
-      <c r="E30" t="s">
-        <v>14</v>
-      </c>
       <c r="F30" t="s">
         <v>14</v>
-      </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
       </c>
       <c r="J30" t="s">
         <v>14</v>
@@ -1504,10 +1501,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
         <v>70</v>
-      </c>
-      <c r="B31" t="s">
-        <v>71</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
@@ -1518,30 +1515,21 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
-      <c r="D32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="I32" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
         <v>74</v>
@@ -1549,8 +1537,23 @@
       <c r="C33" t="s">
         <v>13</v>
       </c>
-      <c r="I33" t="s">
-        <v>15</v>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -1563,7 +1566,22 @@
       <c r="C34" t="s">
         <v>13</v>
       </c>
-      <c r="I34" t="s">
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1577,22 +1595,7 @@
       <c r="C35" t="s">
         <v>13</v>
       </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" t="s">
-        <v>14</v>
-      </c>
-      <c r="K35" t="s">
+      <c r="I35" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1609,6 +1612,9 @@
       <c r="D36" t="s">
         <v>14</v>
       </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
@@ -1616,6 +1622,9 @@
         <v>14</v>
       </c>
       <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
         <v>14</v>
       </c>
       <c r="J36" t="s">
@@ -1635,77 +1644,28 @@
       <c r="C37" t="s">
         <v>13</v>
       </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
       <c r="I37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" t="s">
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D505BD71-3741-414F-932E-9D79F8F86E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB85678F-BE7F-4934-86C7-39DB92CF5FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 11-03-2026'!$A$1:$K$37</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 20-03-2026'!$A$1:$K$37</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB85678F-BE7F-4934-86C7-39DB92CF5FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5578F0-C785-4E49-B0FA-F8CF43310831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 20-03-2026'!$A$1:$K$37</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 25-03-2026'!$A$1:$K$37</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5578F0-C785-4E49-B0FA-F8CF43310831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCBEBD6-B059-4D11-BB17-1691B512A80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 25-03-2026'!$A$1:$K$37</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 08-04-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="88">
   <si>
     <t>Standard</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>WinPLC _LPS_ (EG)</t>
+  </si>
+  <si>
+    <t>Xmedicus _LPS_ (Xmedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -123,6 +126,19 @@
   </si>
   <si>
     <t>CTL03 (C0330Q)</t>
+  </si>
+  <si>
+    <t>Den Dynamiske Blanket</t>
+  </si>
+  <si>
+    <t>DDB (1.1)</t>
+  </si>
+  <si>
+    <t>Den Gode Blanketservice</t>
+  </si>
+  <si>
+    <t>DGB (0.91_x000D_
+0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>
@@ -614,10 +630,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,1022 +667,1071 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
       <c r="J3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
         <v>14</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s">
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>14</v>
-      </c>
-      <c r="K28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
       </c>
       <c r="J29" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
       </c>
       <c r="J30" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="J31" t="s">
+        <v>15</v>
+      </c>
+      <c r="L31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" t="s">
-        <v>14</v>
-      </c>
-      <c r="K33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="I33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>14</v>
-      </c>
-      <c r="K36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" t="s">
         <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="L38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCBEBD6-B059-4D11-BB17-1691B512A80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7B000F-97CE-417E-8501-CAED8510731A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 08-04-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 10-04-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7B000F-97CE-417E-8501-CAED8510731A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D39A094-3ED6-443D-9611-FA28C8458190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
@@ -137,8 +137,7 @@
     <t>Den Gode Blanketservice</t>
   </si>
   <si>
-    <t>DGB (0.91_x000D_
-0.91)</t>
+    <t>DGB (0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D39A094-3ED6-443D-9611-FA28C8458190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAF90D1-E6A6-4BBB-81BC-928712333F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 10-04-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 14-04-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAF90D1-E6A6-4BBB-81BC-928712333F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DC6684-147E-4995-A630-A9DA357CF2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 14-04-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 24-04-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DC6684-147E-4995-A630-A9DA357CF2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A14D7C-F948-4F8B-84A2-FA82D2557650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A14D7C-F948-4F8B-84A2-FA82D2557650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B334D3FF-9625-4A2D-B48D-191E6D8D63A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 24-04-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 27-04-2026'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="87">
   <si>
     <t>Standard</t>
   </si>
@@ -100,11 +100,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
-  </si>
-  <si>
-    <t>CareCommunication (5.0_x000D_
-5.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Care Plan</t>
@@ -629,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -803,29 +799,29 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" t="s">
-        <v>15</v>
+      <c r="L7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
@@ -833,16 +829,34 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -850,6 +864,9 @@
       <c r="D9" t="s">
         <v>15</v>
       </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
       <c r="F9" t="s">
         <v>15</v>
       </c>
@@ -863,6 +880,9 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
         <v>15</v>
       </c>
       <c r="L9" t="s">
@@ -871,10 +891,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -909,48 +929,24 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
       <c r="K11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -961,76 +957,88 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="K13" t="s">
+      <c r="D13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
@@ -1039,67 +1047,61 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
       <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -1107,19 +1109,37 @@
       <c r="D19" t="s">
         <v>15</v>
       </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
       <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -1143,9 +1163,6 @@
         <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
         <v>15</v>
       </c>
       <c r="L20" t="s">
@@ -1154,10 +1171,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -1181,6 +1198,9 @@
         <v>15</v>
       </c>
       <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
         <v>15</v>
       </c>
       <c r="L21" t="s">
@@ -1189,10 +1209,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -1227,10 +1247,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
@@ -1239,7 +1259,7 @@
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -1248,9 +1268,6 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" t="s">
         <v>15</v>
       </c>
       <c r="J23" t="s">
@@ -1265,7 +1282,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
         <v>59</v>
@@ -1277,7 +1294,7 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -1288,10 +1305,10 @@
       <c r="H24" t="s">
         <v>15</v>
       </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
       <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
         <v>15</v>
       </c>
       <c r="L24" t="s">
@@ -1300,10 +1317,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -1335,10 +1352,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -1370,10 +1387,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -1405,10 +1422,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -1440,19 +1457,16 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
       </c>
       <c r="F29" t="s">
         <v>15</v>
@@ -1475,10 +1489,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -1486,6 +1500,9 @@
       <c r="D30" t="s">
         <v>15</v>
       </c>
+      <c r="E30" t="s">
+        <v>15</v>
+      </c>
       <c r="F30" t="s">
         <v>15</v>
       </c>
@@ -1496,7 +1513,7 @@
         <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1507,10 +1524,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -1518,20 +1535,8 @@
       <c r="D31" t="s">
         <v>15</v>
       </c>
-      <c r="E31" t="s">
-        <v>15</v>
-      </c>
       <c r="F31" t="s">
         <v>15</v>
-      </c>
-      <c r="G31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" t="s">
-        <v>16</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -1542,7 +1547,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
         <v>74</v>
@@ -1550,53 +1555,59 @@
       <c r="C32" t="s">
         <v>14</v>
       </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" t="s">
-        <v>15</v>
+      <c r="I32" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
-      <c r="I34" t="s">
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -1622,53 +1633,59 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" t="s">
-        <v>15</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="I36" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
       <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
@@ -1695,41 +1712,6 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B334D3FF-9625-4A2D-B48D-191E6D8D63A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF5E00E-B06C-4D58-B3E9-B12CDC9616CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 27-04-2026'!$A$1:$L$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 06-05-2026'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF5E00E-B06C-4D58-B3E9-B12CDC9616CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CF115A-6D05-42B4-BC52-667A8DF3822C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 06-05-2026'!$A$1:$L$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 01-06-2026'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CF115A-6D05-42B4-BC52-667A8DF3822C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6292E8F-CCAC-4913-8E76-00B61712B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 01-06-2026'!$A$1:$L$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 02-06-2026'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6292E8F-CCAC-4913-8E76-00B61712B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1C85E3-4CCE-4E9D-BD7E-3149D94108C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="87">
   <si>
     <t>Standard</t>
   </si>
@@ -1075,6 +1075,9 @@
       <c r="G17" t="s">
         <v>15</v>
       </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1094,6 +1097,9 @@
       </c>
       <c r="H18" t="s">
         <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1C85E3-4CCE-4E9D-BD7E-3149D94108C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF218542-9AF1-49C6-9E39-B58443878365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 02-06-2026'!$A$1:$L$38</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 05-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="89">
   <si>
     <t>Standard</t>
   </si>
@@ -176,6 +176,12 @@
   </si>
   <si>
     <t>DIS91 (D9134L)</t>
+  </si>
+  <si>
+    <t>Share Notes</t>
+  </si>
+  <si>
+    <t>ECN (1.0)</t>
   </si>
   <si>
     <t>FNUX</t>
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -1150,29 +1156,8 @@
       <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
       <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1206,9 +1191,6 @@
       <c r="J21" t="s">
         <v>15</v>
       </c>
-      <c r="K21" t="s">
-        <v>15</v>
-      </c>
       <c r="L21" t="s">
         <v>15</v>
       </c>
@@ -1265,7 +1247,7 @@
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -1274,6 +1256,9 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s">
         <v>15</v>
       </c>
       <c r="J23" t="s">
@@ -1288,10 +1273,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -1300,7 +1285,7 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -1311,10 +1296,10 @@
       <c r="H24" t="s">
         <v>15</v>
       </c>
-      <c r="I24" t="s">
-        <v>15</v>
-      </c>
       <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
         <v>15</v>
       </c>
       <c r="L24" t="s">
@@ -1323,7 +1308,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
         <v>61</v>
@@ -1474,6 +1459,9 @@
       <c r="D29" t="s">
         <v>15</v>
       </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
       <c r="F29" t="s">
         <v>15</v>
       </c>
@@ -1506,9 +1494,6 @@
       <c r="D30" t="s">
         <v>15</v>
       </c>
-      <c r="E30" t="s">
-        <v>15</v>
-      </c>
       <c r="F30" t="s">
         <v>15</v>
       </c>
@@ -1519,7 +1504,7 @@
         <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1541,8 +1526,20 @@
       <c r="D31" t="s">
         <v>15</v>
       </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
       <c r="F31" t="s">
         <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>16</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -1553,21 +1550,30 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
-      <c r="I32" t="s">
-        <v>16</v>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
         <v>76</v>
@@ -1576,7 +1582,7 @@
         <v>14</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -1589,22 +1595,7 @@
       <c r="C34" t="s">
         <v>14</v>
       </c>
-      <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
-      </c>
-      <c r="L34" t="s">
+      <c r="I34" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1647,7 +1638,22 @@
       <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="I36" t="s">
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1661,28 +1667,7 @@
       <c r="C37" t="s">
         <v>14</v>
       </c>
-      <c r="D37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
       <c r="I37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1718,6 +1703,41 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E222523-238B-4EA9-9BF0-AC26FDEDC45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0909B54-F01C-414B-9942-8AF3B352807F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00452588-2879-46E8-8E46-B1C747ABCBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D01978-F3BB-4432-A14C-5200ADFA829C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D01978-F3BB-4432-A14C-5200ADFA829C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2470475-1701-47D4-863F-3017373B2957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2470475-1701-47D4-863F-3017373B2957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB4954-42D0-41DA-929C-A0ADD57D30FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 09-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 15-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -632,9 +632,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -794,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -825,7 +825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -895,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -975,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB4954-42D0-41DA-929C-A0ADD57D30FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCFC33A-84DB-48A9-9099-8E59D164FFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 15-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 22-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCFC33A-84DB-48A9-9099-8E59D164FFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06736EC-8BB3-4DB3-BAB8-58D15CC1BD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 22-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 23-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -632,9 +632,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -794,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -825,7 +825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -895,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -975,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06736EC-8BB3-4DB3-BAB8-58D15CC1BD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CEFC1E-61C4-4097-8318-0E30C313C3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCFC33A-84DB-48A9-9099-8E59D164FFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E2B052-614A-4AA8-9D08-FEB8CB1EEAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 22-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 23-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E2B052-614A-4AA8-9D08-FEB8CB1EEAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9AC6D7-9B4C-4FBA-8385-D5395C5B0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 23-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 25-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9AC6D7-9B4C-4FBA-8385-D5395C5B0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABEF40A-272E-42C0-B796-FBEC1E592076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 25-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 30-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABEF40A-272E-42C0-B796-FBEC1E592076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCA3218-CE65-4238-8202-8D8A2CA95BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCA3218-CE65-4238-8202-8D8A2CA95BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B87A78-F3D2-4FA8-AF24-D36BA86820C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 30-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 01-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -632,9 +632,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -794,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -825,7 +825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -895,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -975,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B87A78-F3D2-4FA8-AF24-D36BA86820C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC82A1-E2D1-4E3E-B9A7-38961B07B8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 01-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 02-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B87A78-F3D2-4FA8-AF24-D36BA86820C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF50D56-AF28-440E-AA37-A6E10E95C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 01-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 03-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -632,9 +632,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -794,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -825,7 +825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -895,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -975,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC82A1-E2D1-4E3E-B9A7-38961B07B8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7D2685-44D6-4DDA-A09C-4BF30735F635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 02-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 03-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -632,9 +632,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -794,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -825,7 +825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -895,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -975,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7D2685-44D6-4DDA-A09C-4BF30735F635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE140B0-5952-483A-8192-E72E53B75CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 03-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 09-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE140B0-5952-483A-8192-E72E53B75CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4436A1F8-3DCC-47AE-AA5B-0F304385AFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 09-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 19-08-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1082,7 +1082,7 @@
         <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4436A1F8-3DCC-47AE-AA5B-0F304385AFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F71276-0DE1-4C22-ACC5-DF65B2229723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 19-08-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 21-08-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -632,9 +632,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -794,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -825,7 +825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -895,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -975,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F71276-0DE1-4C22-ACC5-DF65B2229723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2166FE1-DC32-473C-9607-DADD0DA118B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 21-08-2026'!$A$1:$L$39</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 27-08-2026'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="91">
   <si>
     <t>Standard</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>FNUX (3.0)</t>
+  </si>
+  <si>
+    <t>RehabilitationPlan</t>
+  </si>
+  <si>
+    <t>GGOP (GGOP100)</t>
   </si>
   <si>
     <t>Sygehushenvisning</t>
@@ -631,10 +637,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -689,7 +695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -724,7 +730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -759,7 +765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -794,7 +800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -811,7 +817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -825,7 +831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -857,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -895,7 +901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -947,7 +953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -961,7 +967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -975,7 +981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1007,7 +1013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1030,7 +1036,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1108,7 +1114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1195,7 +1201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1205,35 +1211,11 @@
       <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
       <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1271,7 +1253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1285,65 +1267,68 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
         <v>16</v>
       </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>61</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>62</v>
       </c>
       <c r="B26" t="s">
         <v>63</v>
@@ -1376,7 +1361,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1411,7 +1396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1481,7 +1466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1494,6 +1479,9 @@
       <c r="D30" t="s">
         <v>15</v>
       </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
       <c r="F30" t="s">
         <v>15</v>
       </c>
@@ -1513,7 +1501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1526,9 +1514,6 @@
       <c r="D31" t="s">
         <v>15</v>
       </c>
-      <c r="E31" t="s">
-        <v>15</v>
-      </c>
       <c r="F31" t="s">
         <v>15</v>
       </c>
@@ -1539,7 +1524,7 @@
         <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -1548,7 +1533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1561,9 +1546,21 @@
       <c r="D32" t="s">
         <v>15</v>
       </c>
+      <c r="E32" t="s">
+        <v>15</v>
+      </c>
       <c r="F32" t="s">
         <v>15</v>
       </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>16</v>
+      </c>
       <c r="J32" t="s">
         <v>15</v>
       </c>
@@ -1571,23 +1568,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>77</v>
       </c>
       <c r="B34" t="s">
         <v>78</v>
@@ -1596,10 +1602,10 @@
         <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1609,26 +1615,11 @@
       <c r="C35" t="s">
         <v>14</v>
       </c>
-      <c r="D35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>15</v>
-      </c>
-      <c r="L35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1657,7 +1648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1667,11 +1658,26 @@
       <c r="C37" t="s">
         <v>14</v>
       </c>
-      <c r="I37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1681,32 +1687,11 @@
       <c r="C38" t="s">
         <v>14</v>
       </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
       <c r="I38" t="s">
         <v>15</v>
       </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1738,6 +1723,41 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2166FE1-DC32-473C-9607-DADD0DA118B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA630CE3-3A14-40A7-9C3A-33A6484CC5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 27-08-2026'!$A$1:$L$40</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 02-09-2026'!$A$1:$M$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="97">
   <si>
     <t>Standard</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Clinea _LPS_ (EG)</t>
   </si>
   <si>
+    <t>DokuDok (DokuDok)</t>
+  </si>
+  <si>
     <t>Journal _LPS_ (DMDC)</t>
   </si>
   <si>
@@ -265,7 +268,22 @@
     <t>Den gode VANSEnvelope</t>
   </si>
   <si>
+    <t>VANSEnvelope (1.0)</t>
+  </si>
+  <si>
     <t>VANSEnvelope (1.0.4)</t>
+  </si>
+  <si>
+    <t>BinaryLetter</t>
+  </si>
+  <si>
+    <t>XBIN01 (XB0131X)</t>
+  </si>
+  <si>
+    <t>ReferralAttachment</t>
+  </si>
+  <si>
+    <t>XBIN02 (XB0210X)</t>
   </si>
   <si>
     <t>NegativeReceipt</t>
@@ -637,10 +655,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -677,978 +695,1017 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I14" t="s">
         <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s">
         <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
       </c>
       <c r="I18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K21" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>62</v>
       </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" t="s">
-        <v>15</v>
-      </c>
-      <c r="K25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>61</v>
-      </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
-      </c>
-      <c r="L26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K26" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
-      </c>
-      <c r="L28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K28" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K29" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K30" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" t="s">
-        <v>15</v>
-      </c>
-      <c r="L31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K31" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I32" t="s">
         <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>77</v>
       </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
-        <v>15</v>
-      </c>
-      <c r="L33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>76</v>
-      </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>81</v>
       </c>
       <c r="B36" t="s">
         <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" t="s">
         <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>15</v>
-      </c>
-      <c r="L36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1656,28 +1713,13 @@
         <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1685,13 +1727,13 @@
         <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1699,34 +1741,31 @@
         <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K39" t="s">
+        <v>16</v>
+      </c>
+      <c r="M39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1734,31 +1773,118 @@
         <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>15</v>
-      </c>
-      <c r="L40" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="K40" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA630CE3-3A14-40A7-9C3A-33A6484CC5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723D6F87-1C98-4310-A595-60E7801FA063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 02-09-2026'!$A$1:$M$43</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 06-09-2026'!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="101">
   <si>
     <t>Standard</t>
   </si>
@@ -163,6 +163,12 @@
     <t>DIS07 (D0734L)</t>
   </si>
   <si>
+    <t>Psykologepikrise</t>
+  </si>
+  <si>
+    <t>DIS10 (D1034L)</t>
+  </si>
+  <si>
     <t>Bookingsvar</t>
   </si>
   <si>
@@ -254,6 +260,12 @@
   </si>
   <si>
     <t>RUC02 (U0231U)</t>
+  </si>
+  <si>
+    <t>Psykologafregning</t>
+  </si>
+  <si>
+    <t>RUC10 (U1031U)</t>
   </si>
   <si>
     <t>Sundhedsjournal</t>
@@ -655,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1126,14 +1138,8 @@
       <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" t="s">
-        <v>16</v>
-      </c>
       <c r="J17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1146,17 +1152,14 @@
       <c r="C18" t="s">
         <v>15</v>
       </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1172,29 +1175,14 @@
       <c r="D19" t="s">
         <v>16</v>
       </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
       <c r="G19" t="s">
         <v>16</v>
       </c>
-      <c r="H19" t="s">
-        <v>16</v>
-      </c>
       <c r="I19" t="s">
         <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
-      </c>
-      <c r="K19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19" t="s">
-        <v>16</v>
-      </c>
-      <c r="M19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -1207,8 +1195,32 @@
       <c r="C20" t="s">
         <v>15</v>
       </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="J20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -1221,32 +1233,8 @@
       <c r="C21" t="s">
         <v>15</v>
       </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" t="s">
-        <v>16</v>
-      </c>
       <c r="I21" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" t="s">
-        <v>16</v>
-      </c>
-      <c r="K21" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -1259,8 +1247,32 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>16</v>
+      </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="K22" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -1273,35 +1285,8 @@
       <c r="C23" t="s">
         <v>15</v>
       </c>
-      <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s">
-        <v>16</v>
-      </c>
       <c r="J23" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" t="s">
-        <v>16</v>
-      </c>
-      <c r="L23" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -1358,8 +1343,11 @@
       <c r="D25" t="s">
         <v>16</v>
       </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
         <v>16</v>
@@ -1368,6 +1356,9 @@
         <v>16</v>
       </c>
       <c r="I25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" t="s">
         <v>16</v>
       </c>
       <c r="K25" t="s">
@@ -1382,10 +1373,10 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
@@ -1393,11 +1384,8 @@
       <c r="D26" t="s">
         <v>16</v>
       </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
         <v>16</v>
@@ -1408,10 +1396,10 @@
       <c r="I26" t="s">
         <v>16</v>
       </c>
-      <c r="J26" t="s">
-        <v>16</v>
-      </c>
       <c r="K26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" t="s">
         <v>16</v>
       </c>
       <c r="M26" t="s">
@@ -1420,7 +1408,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
         <v>66</v>
@@ -1586,6 +1574,9 @@
       <c r="E31" t="s">
         <v>17</v>
       </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" t="s">
         <v>16</v>
       </c>
@@ -1618,8 +1609,8 @@
       <c r="D32" t="s">
         <v>16</v>
       </c>
-      <c r="F32" t="s">
-        <v>16</v>
+      <c r="E32" t="s">
+        <v>17</v>
       </c>
       <c r="G32" t="s">
         <v>16</v>
@@ -1631,7 +1622,7 @@
         <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>
@@ -1653,8 +1644,20 @@
       <c r="D33" t="s">
         <v>16</v>
       </c>
+      <c r="F33" t="s">
+        <v>16</v>
+      </c>
       <c r="G33" t="s">
         <v>16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
       </c>
       <c r="K33" t="s">
         <v>16</v>
@@ -1665,10 +1668,10 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
         <v>15</v>
@@ -1679,38 +1682,47 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
       </c>
-      <c r="E35" t="s">
-        <v>17</v>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -1721,7 +1733,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
         <v>86</v>
@@ -1729,8 +1741,8 @@
       <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="E38" t="s">
-        <v>17</v>
+      <c r="J38" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -1743,26 +1755,8 @@
       <c r="C39" t="s">
         <v>15</v>
       </c>
-      <c r="D39" t="s">
-        <v>16</v>
-      </c>
       <c r="E39" t="s">
         <v>17</v>
-      </c>
-      <c r="G39" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -1775,26 +1769,8 @@
       <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="D40" t="s">
-        <v>16</v>
-      </c>
       <c r="E40" t="s">
         <v>17</v>
-      </c>
-      <c r="G40" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" t="s">
-        <v>16</v>
-      </c>
-      <c r="K40" t="s">
-        <v>16</v>
-      </c>
-      <c r="M40" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -1807,7 +1783,25 @@
       <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="J41" t="s">
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" t="s">
+        <v>16</v>
+      </c>
+      <c r="M41" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1827,9 +1821,6 @@
       <c r="E42" t="s">
         <v>17</v>
       </c>
-      <c r="F42" t="s">
-        <v>20</v>
-      </c>
       <c r="G42" t="s">
         <v>16</v>
       </c>
@@ -1837,9 +1828,6 @@
         <v>16</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" t="s">
         <v>16</v>
       </c>
       <c r="K42" t="s">
@@ -1859,31 +1847,83 @@
       <c r="C43" t="s">
         <v>15</v>
       </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="J43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" t="s">
         <v>20</v>
       </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" t="s">
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" t="s">
         <v>16</v>
       </c>
     </row>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723D6F87-1C98-4310-A595-60E7801FA063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE698880-3ED2-4126-8E37-5A5DEAF46894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE698880-3ED2-4126-8E37-5A5DEAF46894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438EA222-FC0E-41D3-B7D0-71F8F68915F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 06-09-2026'!$A$1:$M$45</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 07-09-2026'!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="101">
   <si>
     <t>Standard</t>
   </si>
@@ -187,12 +187,6 @@
     <t>DIS91 (D9134L)</t>
   </si>
   <si>
-    <t>Share Notes</t>
-  </si>
-  <si>
-    <t>ECN (1.0)</t>
-  </si>
-  <si>
     <t>FNUX</t>
   </si>
   <si>
@@ -266,6 +260,12 @@
   </si>
   <si>
     <t>RUC10 (U1031U)</t>
+  </si>
+  <si>
+    <t>Shared Notes</t>
+  </si>
+  <si>
+    <t>Shared Notes (1.0)</t>
   </si>
   <si>
     <t>Sundhedsjournal</t>
@@ -1233,8 +1233,32 @@
       <c r="C21" t="s">
         <v>15</v>
       </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="J21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -1247,32 +1271,8 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" t="s">
-        <v>16</v>
-      </c>
       <c r="J22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -1285,8 +1285,35 @@
       <c r="C23" t="s">
         <v>15</v>
       </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>16</v>
+      </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="K23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L23" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -1343,11 +1370,8 @@
       <c r="D25" t="s">
         <v>16</v>
       </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
         <v>16</v>
@@ -1356,9 +1380,6 @@
         <v>16</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" t="s">
         <v>16</v>
       </c>
       <c r="K25" t="s">
@@ -1373,19 +1394,22 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
         <v>64</v>
       </c>
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
       <c r="C26" t="s">
         <v>15</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
       </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
         <v>16</v>
@@ -1396,10 +1420,10 @@
       <c r="I26" t="s">
         <v>16</v>
       </c>
+      <c r="J26" t="s">
+        <v>16</v>
+      </c>
       <c r="K26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L26" t="s">
         <v>16</v>
       </c>
       <c r="M26" t="s">
@@ -1408,7 +1432,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
         <v>66</v>
@@ -1574,9 +1598,6 @@
       <c r="E31" t="s">
         <v>17</v>
       </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
       <c r="G31" t="s">
         <v>16</v>
       </c>
@@ -1609,8 +1630,8 @@
       <c r="D32" t="s">
         <v>16</v>
       </c>
-      <c r="E32" t="s">
-        <v>17</v>
+      <c r="F32" t="s">
+        <v>16</v>
       </c>
       <c r="G32" t="s">
         <v>16</v>
@@ -1622,7 +1643,7 @@
         <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>
@@ -1641,29 +1662,8 @@
       <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s">
-        <v>16</v>
-      </c>
       <c r="J33" t="s">
         <v>17</v>
-      </c>
-      <c r="K33" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -1676,7 +1676,10 @@
       <c r="C34" t="s">
         <v>15</v>
       </c>
-      <c r="J34" t="s">
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" t="s">
         <v>17</v>
       </c>
     </row>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438EA222-FC0E-41D3-B7D0-71F8F68915F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11EDF20-28EB-4900-8700-4851ED978916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 07-09-2026'!$A$1:$M$45</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 09-09-2026'!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="101">
   <si>
     <t>Standard</t>
   </si>
@@ -1060,9 +1060,6 @@
       <c r="I14" t="s">
         <v>16</v>
       </c>
-      <c r="J14" t="s">
-        <v>17</v>
-      </c>
       <c r="K14" t="s">
         <v>16</v>
       </c>
@@ -1118,9 +1115,6 @@
       <c r="I16" t="s">
         <v>16</v>
       </c>
-      <c r="J16" t="s">
-        <v>17</v>
-      </c>
       <c r="K16" t="s">
         <v>16</v>
       </c>
@@ -1158,9 +1152,6 @@
       <c r="H18" t="s">
         <v>16</v>
       </c>
-      <c r="J18" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1641,9 +1632,6 @@
       </c>
       <c r="I32" t="s">
         <v>16</v>
-      </c>
-      <c r="J32" t="s">
-        <v>17</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11EDF20-28EB-4900-8700-4851ED978916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F93D96-3462-4580-B84B-6790FD6D1CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 09-09-2026'!$A$1:$M$45</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 09-09-2026'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="95">
   <si>
     <t>Standard</t>
   </si>
@@ -163,12 +163,6 @@
     <t>DIS07 (D0734L)</t>
   </si>
   <si>
-    <t>Psykologepikrise</t>
-  </si>
-  <si>
-    <t>DIS10 (D1034L)</t>
-  </si>
-  <si>
     <t>Bookingsvar</t>
   </si>
   <si>
@@ -193,12 +187,6 @@
     <t>FNUX (3.0)</t>
   </si>
   <si>
-    <t>RehabilitationPlan</t>
-  </si>
-  <si>
-    <t>GGOP (GGOP100)</t>
-  </si>
-  <si>
     <t>Sygehushenvisning</t>
   </si>
   <si>
@@ -254,12 +242,6 @@
   </si>
   <si>
     <t>RUC02 (U0231U)</t>
-  </si>
-  <si>
-    <t>Psykologafregning</t>
-  </si>
-  <si>
-    <t>RUC10 (U1031U)</t>
   </si>
   <si>
     <t>Shared Notes</t>
@@ -667,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1132,8 +1114,11 @@
       <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="J17" t="s">
-        <v>17</v>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1146,11 +1131,17 @@
       <c r="C18" t="s">
         <v>15</v>
       </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" t="s">
-        <v>16</v>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1166,14 +1157,29 @@
       <c r="D19" t="s">
         <v>16</v>
       </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
       <c r="G19" t="s">
         <v>16</v>
       </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
       <c r="I19" t="s">
         <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="K19" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -1189,6 +1195,9 @@
       <c r="D20" t="s">
         <v>16</v>
       </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
       <c r="F20" t="s">
         <v>20</v>
       </c>
@@ -1205,9 +1214,6 @@
         <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" t="s">
         <v>16</v>
       </c>
       <c r="M20" t="s">
@@ -1248,6 +1254,9 @@
       <c r="K21" t="s">
         <v>16</v>
       </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
       <c r="M21" t="s">
         <v>16</v>
       </c>
@@ -1262,8 +1271,35 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>16</v>
+      </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="K22" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -1279,11 +1315,8 @@
       <c r="D23" t="s">
         <v>16</v>
       </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
         <v>16</v>
@@ -1292,9 +1325,6 @@
         <v>16</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" t="s">
         <v>16</v>
       </c>
       <c r="K23" t="s">
@@ -1309,10 +1339,10 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
         <v>60</v>
-      </c>
-      <c r="B24" t="s">
-        <v>61</v>
       </c>
       <c r="C24" t="s">
         <v>15</v>
@@ -1341,28 +1371,28 @@
       <c r="K24" t="s">
         <v>16</v>
       </c>
-      <c r="L24" t="s">
-        <v>16</v>
-      </c>
       <c r="M24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
         <v>62</v>
       </c>
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
       </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
         <v>16</v>
@@ -1373,10 +1403,10 @@
       <c r="I25" t="s">
         <v>16</v>
       </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
       <c r="K25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L25" t="s">
         <v>16</v>
       </c>
       <c r="M25" t="s">
@@ -1385,7 +1415,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
         <v>64</v>
@@ -1513,9 +1543,6 @@
       <c r="E29" t="s">
         <v>17</v>
       </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
       <c r="G29" t="s">
         <v>16</v>
       </c>
@@ -1548,11 +1575,8 @@
       <c r="D30" t="s">
         <v>16</v>
       </c>
-      <c r="E30" t="s">
-        <v>17</v>
-      </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
         <v>16</v>
@@ -1561,9 +1585,6 @@
         <v>16</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" t="s">
         <v>16</v>
       </c>
       <c r="K30" t="s">
@@ -1583,29 +1604,11 @@
       <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
       <c r="I31" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -1621,16 +1624,7 @@
       <c r="D32" t="s">
         <v>16</v>
       </c>
-      <c r="F32" t="s">
-        <v>16</v>
-      </c>
       <c r="G32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s">
         <v>16</v>
       </c>
       <c r="K32" t="s">
@@ -1642,10 +1636,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
         <v>77</v>
-      </c>
-      <c r="B33" t="s">
-        <v>78</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -1656,41 +1650,29 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
         <v>79</v>
       </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
       <c r="C34" t="s">
         <v>15</v>
       </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" t="s">
+      <c r="E34" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
       </c>
-      <c r="D35" t="s">
-        <v>16</v>
-      </c>
-      <c r="G35" t="s">
-        <v>16</v>
-      </c>
-      <c r="K35" t="s">
-        <v>16</v>
-      </c>
-      <c r="M35" t="s">
+      <c r="J35" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1699,21 +1681,21 @@
         <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
-      <c r="J36" t="s">
+      <c r="E36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
         <v>84</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -1724,7 +1706,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
         <v>86</v>
@@ -1732,7 +1714,25 @@
       <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="J38" t="s">
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M38" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1746,8 +1746,26 @@
       <c r="C39" t="s">
         <v>15</v>
       </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
       <c r="E39" t="s">
         <v>17</v>
+      </c>
+      <c r="G39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" t="s">
+        <v>16</v>
+      </c>
+      <c r="M39" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -1760,8 +1778,8 @@
       <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="E40" t="s">
-        <v>17</v>
+      <c r="J40" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -1780,6 +1798,9 @@
       <c r="E41" t="s">
         <v>17</v>
       </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
       <c r="G41" t="s">
         <v>16</v>
       </c>
@@ -1787,6 +1808,9 @@
         <v>16</v>
       </c>
       <c r="I41" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" t="s">
         <v>16</v>
       </c>
       <c r="K41" t="s">
@@ -1812,6 +1836,9 @@
       <c r="E42" t="s">
         <v>17</v>
       </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
       <c r="G42" t="s">
         <v>16</v>
       </c>
@@ -1821,100 +1848,13 @@
       <c r="I42" t="s">
         <v>16</v>
       </c>
+      <c r="J42" t="s">
+        <v>16</v>
+      </c>
       <c r="K42" t="s">
         <v>16</v>
       </c>
       <c r="M42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="J43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" t="s">
-        <v>16</v>
-      </c>
-      <c r="K44" t="s">
-        <v>16</v>
-      </c>
-      <c r="M44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" t="s">
         <v>16</v>
       </c>
     </row>
